--- a/reports/pdf_change_20260806.xlsx
+++ b/reports/pdf_change_20260806.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,232억   ·   현금 115억(2.6%)      당일 2026-08-06  vs  전영업일 2026-08-05      매수 8종목  /  매도 5종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,384억   ·   현금 115억(2.6%)      당일 2026-08-06  vs  전영업일 2026-08-05      매수 8종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>22</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>464983200</v>
+        <v>464076800</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-19</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-1035131400</v>
+        <v>-1033113600</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>17</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>912216600</v>
+        <v>910438400</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-14</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-207559800</v>
+        <v>-207155200</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>16</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>460468800</v>
+        <v>459571200</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-6</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-2326968000</v>
+        <v>-2322432000</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>15</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1675971000</v>
+        <v>1672704000</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -816,23 +816,23 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-191862000</v>
+        <v>-1982464000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>0.52%→0.44%</t>
+          <t>1.04%→0.58%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>43→39</t>
+          <t>9→5</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
         <v>10</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>473499000</v>
+        <v>472576000</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -860,23 +860,23 @@
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1986336000</v>
+        <v>-191488000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>1.04%→0.58%</t>
+          <t>0.52%→0.44%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>9→5</t>
+          <t>43→39</t>
         </is>
       </c>
     </row>
@@ -890,7 +890,7 @@
         <v>7</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>401473800</v>
+        <v>400691200</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>4</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>422712000</v>
+        <v>421888000</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>3</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>393060600</v>
+        <v>392294400</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
     <row r="15" ht="19" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,729억   ·   현금 14억(0.4%)      당일 2026-08-06  vs  전영업일 2026-08-05      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,753억   ·   현금 14억(0.4%)      당일 2026-08-06  vs  전영업일 2026-08-05      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B15" s="4" t="n"/>
@@ -991,7 +991,7 @@
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,367억   ·   현금 50억(2.0%)      당일 2026-08-06  vs  전영업일 2026-08-05      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,439억   ·   현금 49억(2.0%)      당일 2026-08-06  vs  전영업일 2026-08-05      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
@@ -1015,7 +1015,7 @@
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,168억   ·   현금 14억(0.6%)      당일 2026-08-06  vs  전영업일 2026-08-05      매수 1종목  /  매도 1종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,175억   ·   현금 14억(0.6%)      당일 2026-08-06  vs  전영업일 2026-08-05      매수 1종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -1148,7 +1148,7 @@
     <row r="26" ht="19" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 261억   ·   현금 7억(2.6%)      당일 2026-08-06  vs  전영업일 2026-08-05      매수 4종목  /  매도 3종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 268억   ·   현금 7억(2.5%)      당일 2026-08-06  vs  전영업일 2026-08-05      매수 4종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B26" s="4" t="n"/>
@@ -1244,11 +1244,11 @@
         <v>24</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>31860000</v>
+        <v>31626000</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>3.24%→3.36%</t>
+          <t>3.14%→3.26%</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
@@ -1265,11 +1265,11 @@
         <v>-16</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-32580000</v>
+        <v>-35520000</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>2.69%→2.56%</t>
+          <t>2.87%→2.73%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
@@ -1288,11 +1288,11 @@
         <v>15</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>40725000</v>
+        <v>43368750</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>0.95%→1.11%</t>
+          <t>0.99%→1.15%</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
@@ -1309,11 +1309,11 @@
         <v>-11</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-20460000</v>
+        <v>-22522500</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>0.27%→0.19%</t>
+          <t>0.29%→0.20%</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
@@ -1332,11 +1332,11 @@
         <v>14</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>20338500</v>
+        <v>26407500</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>0.08%→0.16%</t>
+          <t>0.10%→0.20%</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
@@ -1353,11 +1353,11 @@
         <v>-8</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-32940000</v>
+        <v>-33540000</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
-          <t>0.89%→0.76%</t>
+          <t>0.88%→0.75%</t>
         </is>
       </c>
       <c r="K31" s="13" t="inlineStr">
@@ -1376,11 +1376,11 @@
         <v>6</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>27855000</v>
+        <v>29925000</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>0.96%→1.07%</t>
+          <t>1.01%→1.13%</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
@@ -1397,7 +1397,7 @@
     <row r="34" ht="19" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 501억   ·   현금 14억(2.8%)      당일 2026-08-06  vs  전영업일 2026-08-05      매수 3종목  /  매도 2종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 504억   ·   현금 14억(2.8%)      당일 2026-08-06  vs  전영업일 2026-08-05      매수 3종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B34" s="4" t="n"/>

--- a/reports/pdf_change_20260806.xlsx
+++ b/reports/pdf_change_20260806.xlsx
@@ -816,23 +816,23 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1982464000</v>
+        <v>-191488000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>1.04%→0.58%</t>
+          <t>0.52%→0.44%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>9→5</t>
+          <t>43→39</t>
         </is>
       </c>
     </row>
@@ -860,23 +860,23 @@
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-191488000</v>
+        <v>-1982464000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>0.52%→0.44%</t>
+          <t>1.04%→0.58%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>43→39</t>
+          <t>9→5</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_change_20260806.xlsx
+++ b/reports/pdf_change_20260806.xlsx
@@ -816,23 +816,23 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-191488000</v>
+        <v>-1982464000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>0.52%→0.44%</t>
+          <t>1.04%→0.58%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>43→39</t>
+          <t>9→5</t>
         </is>
       </c>
     </row>
@@ -860,23 +860,23 @@
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1982464000</v>
+        <v>-191488000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>1.04%→0.58%</t>
+          <t>0.52%→0.44%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>9→5</t>
+          <t>43→39</t>
         </is>
       </c>
     </row>
